--- a/survey_templates/031_wellness_coaching_interest_survey--survey_templates.xlsx
+++ b/survey_templates/031_wellness_coaching_interest_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>coaching_goals</t>
+          <t>coaching_goals_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Coaching goals</t>
+          <t>Coaching Goals 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>coaching_style</t>
+          <t>coaching_style_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Coaching style</t>
+          <t>Coaching Style 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>coaching_goals</t>
+          <t>coaching_goals_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Coaching goals</t>
+          <t>Coaching Goals 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2118,7 +2118,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>coaching_goals_choices</t>
+          <t>coaching_goals_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2135,7 +2135,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>coaching_goals_choices</t>
+          <t>coaching_goals_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2152,7 +2152,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>coaching_goals_choices</t>
+          <t>coaching_goals_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>coaching_style_choices</t>
+          <t>coaching_style_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2288,7 +2288,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>coaching_style_choices</t>
+          <t>coaching_style_2_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>coaching_style_choices</t>
+          <t>coaching_style_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2373,7 +2373,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>coaching_goals_choices</t>
+          <t>coaching_goals_3_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>coaching_goals_choices</t>
+          <t>coaching_goals_3_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2407,7 +2407,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>coaching_goals_choices</t>
+          <t>coaching_goals_3_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
